--- a/data/trans_orig/IP24_R_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP24_R_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>21171</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14440</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>29566</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>17,32%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>11,81%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>24,18%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>17272</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>11541</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>27515</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>16,53%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11,05%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>26,34%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>21186</t>
+          <t>15272</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14839</t>
+          <t>9902</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29366</t>
+          <t>22603</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>36444</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29303</t>
+          <t>27951</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50658</t>
+          <t>47799</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>101081</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>92686</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>107812</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>82,68%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>75,82%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>88,19%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>87190</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>76947</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>92921</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>83,47%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>73,66%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>88,95%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>115332</t>
+          <t>87655</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>107152</t>
+          <t>80324</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>121679</t>
+          <t>93025</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>202521</t>
+          <t>188735</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>190321</t>
+          <t>177380</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>211676</t>
+          <t>197228</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,59%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122252</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122252</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122252</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136518</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136518</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136518</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>240979</t>
+          <t>225179</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>240979</t>
+          <t>225179</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>240979</t>
+          <t>225179</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12119</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7354</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18534</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>13,32%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8,08%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>20,37%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>7541</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4095</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>12106</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>8,01%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>12,86%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12654</t>
+          <t>7569</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7609</t>
+          <t>4397</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19272</t>
+          <t>12130</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>20195</t>
+          <t>19688</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14013</t>
+          <t>13410</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28191</t>
+          <t>27417</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>78861</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>72446</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>83626</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>86,68%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>79,63%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>91,92%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>86575</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>82010</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>90021</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>91,99%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>87,14%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,65%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>82389</t>
+          <t>88485</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>75771</t>
+          <t>83924</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>87434</t>
+          <t>91657</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>168964</t>
+          <t>167345</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>160968</t>
+          <t>159616</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>175146</t>
+          <t>173623</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,83%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>90980</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>90980</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>90980</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>94116</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>94116</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>94116</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>95043</t>
+          <t>96054</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>95043</t>
+          <t>96054</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>95043</t>
+          <t>96054</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>189159</t>
+          <t>187033</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>189159</t>
+          <t>187033</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>189159</t>
+          <t>187033</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7395</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3796</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12945</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13,14%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,74%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>22,99%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4672</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2210</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8492</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,01%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,26%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16,37%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3483</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12268</t>
+          <t>8791</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>11977</t>
+          <t>12178</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7374</t>
+          <t>7265</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18259</t>
+          <t>18411</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>48902</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>43352</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>52501</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>86,86%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>77,01%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93,26%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>47189</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>43369</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>49651</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>90,99%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>83,63%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,74%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>55782</t>
+          <t>48699</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50819</t>
+          <t>44691</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59604</t>
+          <t>51545</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>102971</t>
+          <t>97601</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>96689</t>
+          <t>91368</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>107574</t>
+          <t>102514</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,38%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>56297</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>56297</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>56297</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>63087</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63087</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63087</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>114948</t>
+          <t>109779</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>114948</t>
+          <t>109779</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>114948</t>
+          <t>109779</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>26714</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>19169</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>36875</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13,36%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9,58%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>18,44%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>12895</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6869</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>19320</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>5,94%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,9%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28765</t>
+          <t>13327</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20672</t>
+          <t>8778</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39318</t>
+          <t>18785</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>41660</t>
+          <t>40041</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29563</t>
+          <t>31153</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53442</t>
+          <t>51164</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>173312</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>163151</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>180857</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>86,64%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>81,56%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>90,42%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>204170</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>197745</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>210196</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>94,06%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>91,1%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,84%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>187313</t>
+          <t>164668</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>176760</t>
+          <t>159210</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>195406</t>
+          <t>169217</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>391483</t>
+          <t>337981</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>379701</t>
+          <t>326858</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>403580</t>
+          <t>346869</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>91,76%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>200026</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>200026</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>200026</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>217065</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>217065</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>217065</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>216078</t>
+          <t>177995</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>216078</t>
+          <t>177995</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>216078</t>
+          <t>177995</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>433143</t>
+          <t>378022</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>433143</t>
+          <t>378022</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>433143</t>
+          <t>378022</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>15516</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8664</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>25015</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>10,49%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,86%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>16,91%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>8844</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>4801</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>14878</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7,41%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,46%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>15152</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9441</t>
+          <t>4846</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26140</t>
+          <t>15354</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>23997</t>
+          <t>24829</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16595</t>
+          <t>17142</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35651</t>
+          <t>35239</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>132429</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>122930</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>139281</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>89,51%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>83,09%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>94,14%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>110584</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>104550</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>114627</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>92,59%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>87,54%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>95,98%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>147069</t>
+          <t>109418</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>136081</t>
+          <t>103377</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>152780</t>
+          <t>113885</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>257653</t>
+          <t>241847</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>245999</t>
+          <t>231437</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>265055</t>
+          <t>249534</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,57%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>147945</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>147945</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>147945</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>162221</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>162221</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>162221</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>281650</t>
+          <t>266676</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>281650</t>
+          <t>266676</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>281650</t>
+          <t>266676</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>7968</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4079</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>13880</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>11,67%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>5,97%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>20,33%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>4205</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1703</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>8336</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2,47%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>12,1%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7872</t>
+          <t>4343</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3820</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14357</t>
+          <t>8488</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>12077</t>
+          <t>12310</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7187</t>
+          <t>7357</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19318</t>
+          <t>19057</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>60319</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>54407</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>64208</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>88,33%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>79,67%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>94,03%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>64690</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>60559</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>67192</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>93,9%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>87,9%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>97,53%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>64131</t>
+          <t>66013</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>57646</t>
+          <t>61868</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>68183</t>
+          <t>68457</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>128821</t>
+          <t>126334</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>121580</t>
+          <t>119587</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>133711</t>
+          <t>131287</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,69%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>90883</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>76564</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>108486</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>13,25%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>11,16%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>15,82%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>55430</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>44346</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>69945</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>8,45%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>6,76%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>10,67%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>92934</t>
+          <t>54607</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>77270</t>
+          <t>43942</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>111343</t>
+          <t>65641</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>148364</t>
+          <t>145490</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>129066</t>
+          <t>127852</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>171516</t>
+          <t>168070</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>594903</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>577300</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>609222</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>86,75%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>84,18%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>88,84%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>838</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>600397</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>585882</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>611481</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>91,55%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>89,33%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>93,24%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>832</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>652016</t>
+          <t>564939</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>633607</t>
+          <t>553905</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>667680</t>
+          <t>575604</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1252413</t>
+          <t>1159842</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1229261</t>
+          <t>1137262</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1271711</t>
+          <t>1177480</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,21%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>951</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>685786</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>685786</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>685786</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>926</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>655827</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>655827</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>655827</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>951</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>744950</t>
+          <t>619546</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>744950</t>
+          <t>619546</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>744950</t>
+          <t>619546</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1400777</t>
+          <t>1305332</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1400777</t>
+          <t>1305332</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1400777</t>
+          <t>1305332</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
